--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,7 +634,7 @@
 </t>
   </si>
   <si>
-    <t>Responsable et auteur du statut de l'évaluation</t>
+    <t>TDDUI QR Participant</t>
   </si>
   <si>
     <t>Extension permettant d'ajouter le responsable de l'évaluation et l'auteur du statut de l'évaluation dans un QuestionnaireResponse.</t>
@@ -764,7 +764,7 @@
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -783,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t>Commentaire</t>
+    <t>TDDUI Comment</t>
   </si>
   <si>
     <t xml:space="preserve">

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
